--- a/Cyber Hunt.xlsx
+++ b/Cyber Hunt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/270dcdb5046aa350/Documents/GitHub/CyberHunt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8CA96830-F816-4DAD-8043-AB503FE21F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{8CA96830-F816-4DAD-8043-AB503FE21F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDB67A57-464E-4C70-BF2E-3C5D17852C76}"/>
   <bookViews>
     <workbookView xWindow="3420" yWindow="3420" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3448,7 +3448,7 @@
       <c r="D30" s="1" t="s">
         <v>510</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="11" t="s">
         <v>175</v>
       </c>
       <c r="F30" s="1" t="s">
@@ -7677,10 +7677,11 @@
     <hyperlink ref="J86" r:id="rId86" xr:uid="{BF83372A-0950-4941-9A3C-FD5A5AD0889E}"/>
     <hyperlink ref="E87" r:id="rId87" xr:uid="{7BCC727F-6E9B-4244-BE62-B01393FF2C01}"/>
     <hyperlink ref="E86" r:id="rId88" xr:uid="{485E0871-C4DD-45BF-9C04-FDC91808AAF5}"/>
+    <hyperlink ref="E30" r:id="rId89" xr:uid="{BB248E49-4BB6-4B85-9F19-4449D892DFF6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId89"/>
+    <tablePart r:id="rId90"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Cyber Hunt.xlsx
+++ b/Cyber Hunt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/270dcdb5046aa350/Documents/GitHub/CyberHunt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{8CA96830-F816-4DAD-8043-AB503FE21F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BDB67A57-464E-4C70-BF2E-3C5D17852C76}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{8CA96830-F816-4DAD-8043-AB503FE21F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF374159-10E9-466F-80CC-6B8923957C20}"/>
   <bookViews>
     <workbookView xWindow="3420" yWindow="3420" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5835,7 +5835,7 @@
       <c r="D85" s="1" t="s">
         <v>565</v>
       </c>
-      <c r="E85" s="1" t="s">
+      <c r="E85" s="11" t="s">
         <v>472</v>
       </c>
       <c r="F85" s="1" t="s">
@@ -7678,10 +7678,11 @@
     <hyperlink ref="E87" r:id="rId87" xr:uid="{7BCC727F-6E9B-4244-BE62-B01393FF2C01}"/>
     <hyperlink ref="E86" r:id="rId88" xr:uid="{485E0871-C4DD-45BF-9C04-FDC91808AAF5}"/>
     <hyperlink ref="E30" r:id="rId89" xr:uid="{BB248E49-4BB6-4B85-9F19-4449D892DFF6}"/>
+    <hyperlink ref="E85" r:id="rId90" xr:uid="{C55ED96F-6250-41E4-8B3F-CBC2C8485D3A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId90"/>
+    <tablePart r:id="rId91"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Cyber Hunt.xlsx
+++ b/Cyber Hunt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/270dcdb5046aa350/Documents/GitHub/CyberHunt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{8CA96830-F816-4DAD-8043-AB503FE21F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AF374159-10E9-466F-80CC-6B8923957C20}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{8CA96830-F816-4DAD-8043-AB503FE21F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24A79360-A056-4B04-9F95-1F9D87A28B5F}"/>
   <bookViews>
     <workbookView xWindow="3420" yWindow="3420" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4261,7 +4261,7 @@
       <c r="D49" s="1" t="s">
         <v>529</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="11" t="s">
         <v>267</v>
       </c>
       <c r="F49" s="1" t="s">
@@ -7679,10 +7679,11 @@
     <hyperlink ref="E86" r:id="rId88" xr:uid="{485E0871-C4DD-45BF-9C04-FDC91808AAF5}"/>
     <hyperlink ref="E30" r:id="rId89" xr:uid="{BB248E49-4BB6-4B85-9F19-4449D892DFF6}"/>
     <hyperlink ref="E85" r:id="rId90" xr:uid="{C55ED96F-6250-41E4-8B3F-CBC2C8485D3A}"/>
+    <hyperlink ref="E49" r:id="rId91" xr:uid="{8D651921-97C9-40A3-9E1A-985DABE20DCA}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId91"/>
+    <tablePart r:id="rId92"/>
   </tableParts>
 </worksheet>
 </file>
--- a/Cyber Hunt.xlsx
+++ b/Cyber Hunt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/270dcdb5046aa350/Documents/GitHub/CyberHunt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{8CA96830-F816-4DAD-8043-AB503FE21F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{24A79360-A056-4B04-9F95-1F9D87A28B5F}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{8CA96830-F816-4DAD-8043-AB503FE21F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4F35F30-2954-448B-A904-927C5211122E}"/>
   <bookViews>
     <workbookView xWindow="3420" yWindow="3420" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5750,7 +5750,7 @@
       <c r="D83" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="E83" s="1" t="s">
+      <c r="E83" s="11" t="s">
         <v>461</v>
       </c>
       <c r="F83" s="1" t="s">
@@ -7680,10 +7680,11 @@
     <hyperlink ref="E30" r:id="rId89" xr:uid="{BB248E49-4BB6-4B85-9F19-4449D892DFF6}"/>
     <hyperlink ref="E85" r:id="rId90" xr:uid="{C55ED96F-6250-41E4-8B3F-CBC2C8485D3A}"/>
     <hyperlink ref="E49" r:id="rId91" xr:uid="{8D651921-97C9-40A3-9E1A-985DABE20DCA}"/>
+    <hyperlink ref="E83" r:id="rId92" xr:uid="{CDCD3DDA-95E8-468D-97C8-1B942783C8E1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId92"/>
+    <tablePart r:id="rId93"/>
   </tableParts>
 </worksheet>
 </file>